--- a/agriculture 51.xlsx
+++ b/agriculture 51.xlsx
@@ -22,13 +22,13 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="6">
   <si>
-    <t xml:space="preserve">Area(000 ha)</t>
+    <t xml:space="preserve">Area (000 ha)</t>
   </si>
   <si>
     <t xml:space="preserve">Production(million nuts)</t>
   </si>
   <si>
-    <t xml:space="preserve">Productivity( nuts/ha)</t>
+    <t xml:space="preserve">Productivity(nuts/ha)</t>
   </si>
   <si>
     <t xml:space="preserve">Kerala</t>
